--- a/data/trans_orig/P6904-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6904-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29332</t>
+          <t>28416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26123</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42593</t>
+          <t>42944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>17756</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30358</t>
+          <t>30938</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23438</t>
+          <t>23087</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39908</t>
+          <t>39752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56061</t>
+          <t>55948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81011</t>
+          <t>80432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>24573</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41873</t>
+          <t>42544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87943</t>
+          <t>85533</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117629</t>
+          <t>117195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61280</t>
+          <t>61859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86230</t>
+          <t>86343</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37402</t>
+          <t>36731</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54676</t>
+          <t>54702</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103937</t>
+          <t>104371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133623</t>
+          <t>136033</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>61,4%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62439</t>
+          <t>61898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84396</t>
+          <t>83718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31743</t>
+          <t>31649</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47935</t>
+          <t>48467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100130</t>
+          <t>99017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126994</t>
+          <t>127190</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41632</t>
+          <t>42310</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63589</t>
+          <t>64130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22107</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38299</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69076</t>
+          <t>68880</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95940</t>
+          <t>97053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41487</t>
+          <t>42196</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64343</t>
+          <t>64674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29744</t>
+          <t>29179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64701</t>
+          <t>64280</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90805</t>
+          <t>90571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46767</t>
+          <t>46436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69623</t>
+          <t>68914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>19068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57342</t>
+          <t>57576</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83446</t>
+          <t>83867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,61%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34466</t>
+          <t>34482</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24070</t>
+          <t>24867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40045</t>
+          <t>40302</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,4%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24450</t>
+          <t>24336</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>19489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>34924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -2791,97 +2791,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>821</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2904,97 +2904,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>223693</t>
+          <t>222390</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>268198</t>
+          <t>267606</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>100160</t>
+          <t>98975</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>129872</t>
+          <t>128347</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>333659</t>
+          <t>334291</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>386773</t>
+          <t>387206</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>204107</t>
+          <t>204699</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>248612</t>
+          <t>249915</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>90249</t>
+          <t>91774</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119961</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>305654</t>
+          <t>305221</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>358768</t>
+          <t>358136</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2012 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>13194</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>64,73%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16259</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38966</t>
+          <t>37485</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57596</t>
+          <t>56764</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22898</t>
+          <t>23114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39363</t>
+          <t>40169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67420</t>
+          <t>66041</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93226</t>
+          <t>92362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28692</t>
+          <t>29524</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47322</t>
+          <t>48803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26707</t>
+          <t>25901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43172</t>
+          <t>42956</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59132</t>
+          <t>59996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84938</t>
+          <t>86317</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,65%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46877</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65808</t>
+          <t>66072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31385</t>
+          <t>32454</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48839</t>
+          <t>48824</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84727</t>
+          <t>83198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110342</t>
+          <t>109559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>64,6%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31147</t>
+          <t>30883</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50078</t>
+          <t>50769</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23792</t>
+          <t>23807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41246</t>
+          <t>40177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59245</t>
+          <t>60028</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84860</t>
+          <t>86389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35494</t>
+          <t>35162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54681</t>
+          <t>55296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>11769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24767</t>
+          <t>24855</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52544</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75850</t>
+          <t>75776</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,12%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35370</t>
+          <t>34755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54557</t>
+          <t>54889</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28211</t>
+          <t>28552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54522</t>
+          <t>54596</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77828</t>
+          <t>79460</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>60,95%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29246</t>
+          <t>29956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32594</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>47582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>71,64%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>11878</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25030</t>
+          <t>24729</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18096</t>
+          <t>18834</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33822</t>
+          <t>34156</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>160143</t>
+          <t>159921</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>197915</t>
+          <t>196372</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>94801</t>
+          <t>96046</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>124703</t>
+          <t>125458</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>264194</t>
+          <t>265561</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>312849</t>
+          <t>316514</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>127540</t>
+          <t>129083</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>165312</t>
+          <t>165534</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>88958</t>
+          <t>88203</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>118860</t>
+          <t>117615</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>226267</t>
+          <t>222602</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>274922</t>
+          <t>273555</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12452</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>10815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>21167</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>73,51%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18819</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>62,44%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37996</t>
+          <t>38938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57612</t>
+          <t>57308</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22874</t>
+          <t>22368</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35072</t>
+          <t>35013</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67396</t>
+          <t>66223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88503</t>
+          <t>88041</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>68,86%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>24264</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43576</t>
+          <t>42634</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11219</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23417</t>
+          <t>23923</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39360</t>
+          <t>39822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60467</t>
+          <t>61640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62913</t>
+          <t>61528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83369</t>
+          <t>83777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37808</t>
+          <t>37540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53700</t>
+          <t>53930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106023</t>
+          <t>106125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131326</t>
+          <t>132157</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29754</t>
+          <t>29346</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50210</t>
+          <t>51595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33650</t>
+          <t>33918</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53255</t>
+          <t>52424</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78558</t>
+          <t>78456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,5%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41290</t>
+          <t>40503</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60522</t>
+          <t>60001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28378</t>
+          <t>28009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43060</t>
+          <t>43042</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73803</t>
+          <t>73321</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99653</t>
+          <t>98999</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30906</t>
+          <t>31427</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50138</t>
+          <t>50925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13047</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27729</t>
+          <t>28098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47882</t>
+          <t>48536</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73732</t>
+          <t>74214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>20240</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34761</t>
+          <t>34313</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>20573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29712</t>
+          <t>29697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45099</t>
+          <t>46532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62172</t>
+          <t>62262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,31%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13474</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>29114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -8406,97 +8406,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8519,97 +8519,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>1880</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>189336</t>
+          <t>189315</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>227259</t>
+          <t>228223</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>131567</t>
+          <t>131790</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>159313</t>
+          <t>158949</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>330461</t>
+          <t>331123</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>377016</t>
+          <t>377794</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,71%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>122742</t>
+          <t>121778</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160665</t>
+          <t>160686</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56985</t>
+          <t>57349</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84731</t>
+          <t>84508</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>189283</t>
+          <t>188505</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>235838</t>
+          <t>235176</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11326</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14247</t>
+          <t>14214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>18431</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26472</t>
+          <t>26516</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45491</t>
+          <t>45569</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>18734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33475</t>
+          <t>33339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50726</t>
+          <t>50896</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74769</t>
+          <t>75158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32602</t>
+          <t>32558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30983</t>
+          <t>31215</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34253</t>
+          <t>33864</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58296</t>
+          <t>58126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46632</t>
+          <t>48129</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66988</t>
+          <t>68542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36299</t>
+          <t>35571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50792</t>
+          <t>49868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89718</t>
+          <t>88547</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113552</t>
+          <t>112814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28543</t>
+          <t>26989</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48899</t>
+          <t>47402</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24760</t>
+          <t>25684</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39253</t>
+          <t>39981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57532</t>
+          <t>58270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81366</t>
+          <t>82537</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,24%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58281</t>
+          <t>58640</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>78477</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101178</t>
+          <t>100954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134541</t>
+          <t>135238</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163284</t>
+          <t>165117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208868</t>
+          <t>211834</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>80,39%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29374</t>
+          <t>30076</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50272</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20408</t>
+          <t>19711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53771</t>
+          <t>53995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54634</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100218</t>
+          <t>98385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34020</t>
+          <t>33919</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49414</t>
+          <t>48989</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33522</t>
+          <t>33634</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43573</t>
+          <t>43361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71763</t>
+          <t>70796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89776</t>
+          <t>88869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33416</t>
+          <t>33517</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11934</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21985</t>
+          <t>21873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33167</t>
+          <t>34074</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51180</t>
+          <t>52147</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -11385,7 +11385,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,49%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>188867</t>
+          <t>188962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>227692</t>
+          <t>227403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>210530</t>
+          <t>211471</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>266559</t>
+          <t>267993</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>409751</t>
+          <t>410195</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>480048</t>
+          <t>477653</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>111813</t>
+          <t>112102</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>150638</t>
+          <t>150543</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>87656</t>
+          <t>86222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143685</t>
+          <t>142744</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>213672</t>
+          <t>216067</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>283969</t>
+          <t>283525</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
